--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_14_5.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_14_5.xlsx
@@ -517,52 +517,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.998974007186856</v>
+        <v>0.9999608360151518</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6911493182481759</v>
+        <v>0.6985304212648373</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9988397946542386</v>
+        <v>0.9998037380783483</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9997153210340989</v>
+        <v>0.9999230798079892</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9991005771426852</v>
+        <v>0.9998580792833762</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000609073654464036</v>
+        <v>2.324943320192471e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1833471063426455</v>
+        <v>0.1789653647449071</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009062417990762977</v>
+        <v>0.0001095101914724521</v>
       </c>
       <c r="J2" t="n">
-        <v>9.250963266125186e-05</v>
+        <v>3.57987593505182e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004993757158687748</v>
+        <v>7.265501991026756e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008869879743533166</v>
+        <v>0.001884668452431135</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02467941762813775</v>
+        <v>0.004821766605915794</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000911993611683</v>
+        <v>1.000034812430976</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02573007153000492</v>
+        <v>0.00502703919276251</v>
       </c>
       <c r="P2" t="n">
-        <v>116.8071427085535</v>
+        <v>123.3384596092798</v>
       </c>
       <c r="Q2" t="n">
-        <v>178.9698097768317</v>
+        <v>185.5011266775581</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +572,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9989137506134093</v>
+        <v>0.9999608359635856</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6872519825546837</v>
+        <v>0.69853041589098</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9990194229021653</v>
+        <v>0.9998037396786601</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9977845157612457</v>
+        <v>0.9999230774762362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9986618949698036</v>
+        <v>0.9998580804250733</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006448445594104714</v>
+        <v>2.324946381386197e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1856607331664383</v>
+        <v>0.178965367935061</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007659333380260554</v>
+        <v>0.0001095092985307714</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007199465279958458</v>
+        <v>3.579984455144978e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007429399330109506</v>
+        <v>7.265443542884947e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009666396880382965</v>
+        <v>0.001884633352203196</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02539378978038669</v>
+        <v>0.004821769780263463</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000965555010303</v>
+        <v>1.000034812476813</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02647485598372932</v>
+        <v>0.005027042502248731</v>
       </c>
       <c r="P3" t="n">
-        <v>116.6930025267482</v>
+        <v>123.3384569759324</v>
       </c>
       <c r="Q3" t="n">
-        <v>178.8556695950264</v>
+        <v>185.5011240442107</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +627,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9986812330569104</v>
+        <v>0.9999608320589297</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6833393120023439</v>
+        <v>0.6985302565007254</v>
       </c>
       <c r="D4" t="n">
-        <v>0.999113918634903</v>
+        <v>0.9998037196139299</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9941694704665072</v>
+        <v>0.9999230703979027</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9976704477254952</v>
+        <v>0.9998580660071935</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007828770251836641</v>
+        <v>2.325178178628096e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1879834634248744</v>
+        <v>0.1789654625560013</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006921222810833712</v>
+        <v>0.000109520494245271</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001894696166457801</v>
+        <v>3.580313881722006e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001293409240463001</v>
+        <v>7.266181653124555e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01045444023461845</v>
+        <v>0.001884513614567327</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02797993969228069</v>
+        <v>0.004822010139587116</v>
       </c>
       <c r="N4" t="n">
-        <v>1.001172237282746</v>
+        <v>1.000034815947618</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02917110365144098</v>
+        <v>0.005027293094166404</v>
       </c>
       <c r="P4" t="n">
-        <v>116.3050698605352</v>
+        <v>123.3382575857964</v>
       </c>
       <c r="Q4" t="n">
-        <v>178.4677369288135</v>
+        <v>185.5009246540747</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9983081577657645</v>
+        <v>0.9999608320589297</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6794723645587957</v>
+        <v>0.6985302565007254</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9991322612774521</v>
+        <v>0.9998037196139299</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9892028465607834</v>
+        <v>0.9999230703979027</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9962299044137415</v>
+        <v>0.9998580660071935</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001004350634021258</v>
+        <v>2.325178178628096e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1902790504707964</v>
+        <v>0.1789654625560013</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006777947575597471</v>
+        <v>0.000109520494245271</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003508656480071909</v>
+        <v>3.580313881722006e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002093224746258254</v>
+        <v>7.266181653124555e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01136389005645275</v>
+        <v>0.001884513614567327</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03169149150830958</v>
+        <v>0.004822010139587116</v>
       </c>
       <c r="N5" t="n">
-        <v>1.001503859763765</v>
+        <v>1.000034815947618</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03304066391224967</v>
+        <v>0.005027293094166404</v>
       </c>
       <c r="P5" t="n">
-        <v>115.8068281632174</v>
+        <v>123.3382575857964</v>
       </c>
       <c r="Q5" t="n">
-        <v>177.9694952314956</v>
+        <v>185.5009246540747</v>
       </c>
     </row>
     <row r="6">
@@ -737,1097 +737,1097 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9978272471256346</v>
+        <v>0.9999608320589297</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6756995716721205</v>
+        <v>0.6985302565007254</v>
       </c>
       <c r="D6" t="n">
-        <v>0.999086609269411</v>
+        <v>0.9998037196139299</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9832214673085991</v>
+        <v>0.9999230703979027</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9944473797721405</v>
+        <v>0.9998580660071935</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001289839964260363</v>
+        <v>2.325178178628096e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1925187433044935</v>
+        <v>0.1789654625560013</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007134537536589153</v>
+        <v>0.000109520494245271</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005452372959706114</v>
+        <v>3.580313881722006e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003082914425271724</v>
+        <v>7.266181653124555e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0122051394847914</v>
+        <v>0.001884513614567327</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03591434204131217</v>
+        <v>0.004822010139587116</v>
       </c>
       <c r="N6" t="n">
-        <v>1.001931335888325</v>
+        <v>1.000034815947618</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03744328993494787</v>
+        <v>0.005027293094166404</v>
       </c>
       <c r="P6" t="n">
-        <v>115.3064742540347</v>
+        <v>123.3382575857964</v>
       </c>
       <c r="Q6" t="n">
-        <v>177.469141322313</v>
+        <v>185.5009246540747</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_5</t>
+          <t>model_14_5_22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9972716520823247</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6720736473216566</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D7" t="n">
-        <v>0.998991756739673</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9765616267698923</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9924317049193451</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001619665182425273</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1946712486307051</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007875435064002636</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007616563067212282</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004202053286806273</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01296423291039522</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04024506407530336</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N7" t="n">
-        <v>1.002425198149045</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04195837977175655</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P7" t="n">
-        <v>114.8510716572277</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q7" t="n">
-        <v>177.0137387255059</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_6</t>
+          <t>model_14_5_21</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9966733810245434</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6686400385630482</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9988638946476645</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9695450240393627</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9902884045905855</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001974824726288328</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1967095871139903</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008874171819688452</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009896687062592823</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.005392052103593581</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01362973205843367</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04443900005950097</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N8" t="n">
-        <v>1.00295699464485</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04633086029344578</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P8" t="n">
-        <v>114.4545512615007</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q8" t="n">
-        <v>176.617218329779</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_7</t>
+          <t>model_14_5_20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9960600248516435</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6654396344065947</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9987174220884387</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9624464986289268</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9881080390932926</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002338939446128745</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.198609485271522</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001001827580156495</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01220343275445434</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00660263016730542</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01419670787386262</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04836258312092877</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N9" t="n">
-        <v>1.003502200131873</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05042147840873519</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P9" t="n">
-        <v>114.1161153610031</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q9" t="n">
-        <v>176.2787824292814</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_8</t>
+          <t>model_14_5_19</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9954529177754028</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6624952444300014</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9985638218319862</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9554775120607636</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9859605714316861</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002699344432245396</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2003574023526521</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001121805455844267</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01446808334218316</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007794942762096897</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0146673190566914</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05195521564044746</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N10" t="n">
-        <v>1.004041850866309</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05416705673238434</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P10" t="n">
-        <v>113.8294926766506</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q10" t="n">
-        <v>175.9921597449289</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_9</t>
+          <t>model_14_5_18</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9948637197292186</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6597964931930701</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9984106786902989</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9487491353036979</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9838838415003018</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003049117844490612</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2019594976668777</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001241426277060063</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0166545450648904</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008947980499260218</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01506399239996741</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05521881784763788</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N11" t="n">
-        <v>1.004565582462917</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05756959724212278</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P11" t="n">
-        <v>113.5858059230256</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q11" t="n">
-        <v>175.7484729913039</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_10</t>
+          <t>model_14_5_17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9942986861096187</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6573385273398984</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9982605504760709</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9423233076240892</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9818977555013477</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003384546209266629</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2034186523759166</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001358692124395791</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01874269006114419</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01005069109799427</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01545299441056568</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05817685286492067</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N12" t="n">
-        <v>1.005067834569228</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06065356193406793</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P12" t="n">
-        <v>113.377070881811</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q12" t="n">
-        <v>175.5397379500892</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_11</t>
+          <t>model_14_5_16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9937578463013976</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6550938440402476</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9981135084018276</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9361965952107717</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9800013836504703</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003705612082489841</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.204751193347859</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001473547373416127</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02073363418651388</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01110359079126266</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01589978809453329</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06087373885748962</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N13" t="n">
-        <v>1.005548581065424</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06346525994666415</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P13" t="n">
-        <v>113.1958136588563</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q13" t="n">
-        <v>175.3584807271345</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_12</t>
+          <t>model_14_5_15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9932401702446199</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6530360517993186</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9979690949948293</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9303552894343076</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9781903796806323</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G14" t="n">
-        <v>0.004012926952234395</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2059727877140708</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I14" t="n">
-        <v>0.00158634935820868</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02263183221435994</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01210909270454408</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01629233794549989</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06334766729907579</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N14" t="n">
-        <v>1.006008737560338</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06604450864374652</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P14" t="n">
-        <v>113.0364687812908</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q14" t="n">
-        <v>175.199135849569</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_13</t>
+          <t>model_14_5_14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9927445592987701</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6511430930735882</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9978263161063607</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9247876038015345</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9764606018131505</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G15" t="n">
-        <v>0.004307143018968855</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2070965297852235</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I15" t="n">
-        <v>0.00169787461296518</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02444111429823575</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01306949642771228</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01663680712200337</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06562882765194618</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N15" t="n">
-        <v>1.006449280623315</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06842278271549151</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P15" t="n">
-        <v>112.8949609345854</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q15" t="n">
-        <v>175.0576280028637</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_14</t>
+          <t>model_14_5_12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9922678614466027</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6493900991400591</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9976839681452556</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9194582968444689</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9748008905597274</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G16" t="n">
-        <v>0.004590131456290423</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2081371827095613</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001809063268351048</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02617293254963567</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01399099790899336</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01694972379201459</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06775050890060105</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N16" t="n">
-        <v>1.006873012047464</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O16" t="n">
-        <v>0.07063478832738729</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P16" t="n">
-        <v>112.7676932312102</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q16" t="n">
-        <v>174.9303602994885</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_15</t>
+          <t>model_14_5_23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9918082234767585</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6477623742598977</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9975401011702746</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9143483018670439</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9732042873419455</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G17" t="n">
-        <v>0.004862992410516469</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2091034705124788</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00192143843255006</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0278334829059505</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01487746067603773</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01724198770741364</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M17" t="n">
-        <v>0.06973515906998756</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N17" t="n">
-        <v>1.00728157913177</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0727039291632768</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P17" t="n">
-        <v>112.6522026164409</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q17" t="n">
-        <v>174.8148696847192</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_16</t>
+          <t>model_14_5_11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9913622819166253</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6462393902539383</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9973941075896255</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9094191321211572</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9716591054792977</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005127722584283814</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2100075796078997</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I18" t="n">
-        <v>0.002035474698340665</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02943527206895923</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01573537338364995</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01751550785915934</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M18" t="n">
-        <v>0.07160811814510848</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N18" t="n">
-        <v>1.007677971629666</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O18" t="n">
-        <v>0.07465662398378539</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P18" t="n">
-        <v>112.5461873181114</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q18" t="n">
-        <v>174.7088543863897</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_17</t>
+          <t>model_14_5_10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9909278866009149</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6448065416767242</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9972452052188504</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9046464988085287</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9701576828784961</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G19" t="n">
-        <v>0.005385598408590097</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2108581804191696</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I19" t="n">
-        <v>0.002151783033646102</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03098619295691658</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01656899016356509</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01777579064382005</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07338663644417896</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N19" t="n">
-        <v>1.008064100799187</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O19" t="n">
-        <v>0.07651085748888774</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P19" t="n">
-        <v>112.4480536989227</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q19" t="n">
-        <v>174.6107207672009</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_18</t>
+          <t>model_14_5_9</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9905062476781351</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6434562566414396</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9970945155748123</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9000399732693676</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9687036290533122</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G20" t="n">
-        <v>0.005635901487005297</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.211659767945391</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I20" t="n">
-        <v>0.002269487416421231</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J20" t="n">
-        <v>0.03248313525514208</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01737630694894322</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.018023144779813</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M20" t="n">
-        <v>0.07507264140154719</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N20" t="n">
-        <v>1.008438890952769</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O20" t="n">
-        <v>0.07826863916780252</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P20" t="n">
-        <v>112.3571963286763</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q20" t="n">
-        <v>174.5198633969545</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_19</t>
+          <t>model_14_5_8</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9900961870668796</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6421803114252144</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9969413055620024</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8955861124676381</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F21" t="n">
-        <v>0.96729245902378</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G21" t="n">
-        <v>0.005879331179542606</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2124172241437057</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I21" t="n">
-        <v>0.002389160470982299</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J21" t="n">
-        <v>0.03393046742943227</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01815981388117097</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01826109406887648</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M21" t="n">
-        <v>0.07667679687847299</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N21" t="n">
-        <v>1.008803389273885</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O21" t="n">
-        <v>0.07994108686444068</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P21" t="n">
-        <v>112.2726245370336</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q21" t="n">
-        <v>174.4352916053118</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_20</t>
+          <t>model_14_5_7</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9896980314201064</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6409744204481129</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9967862481887925</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8912860399354863</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9659250022279275</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G22" t="n">
-        <v>0.006115693570895563</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2131330931194909</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I22" t="n">
-        <v>0.002510276507355669</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J22" t="n">
-        <v>0.03532782437537639</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.01891905044136603</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01849044001216135</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M22" t="n">
-        <v>0.07820290001589175</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N22" t="n">
-        <v>1.00915730540435</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O22" t="n">
-        <v>0.08153215937188836</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P22" t="n">
-        <v>112.1937941900652</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q22" t="n">
-        <v>174.3564612583434</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_21</t>
+          <t>model_14_5_6</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9893127446062094</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6398370943715086</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9966297191761607</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8871486649983107</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9646041224974109</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G23" t="n">
-        <v>0.006344416467148577</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2138082590084916</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I23" t="n">
-        <v>0.002632542048135404</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03667231090745456</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0196524265787844</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01871185212238673</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M23" t="n">
-        <v>0.07965184534678765</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N23" t="n">
-        <v>1.009499782572258</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O23" t="n">
-        <v>0.08304278930525082</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P23" t="n">
-        <v>112.120360298795</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q23" t="n">
-        <v>174.2830273670733</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_22</t>
+          <t>model_14_5_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9889381068597056</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6387569761470696</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9964719545050321</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8831467459741468</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9633220269912409</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G24" t="n">
-        <v>0.006566817616981226</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2144494638451964</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I24" t="n">
-        <v>0.002755772767521938</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0379727795166952</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.02036426901863212</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01892680636135208</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M24" t="n">
-        <v>0.08103590325887178</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N24" t="n">
-        <v>1.009832793902484</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O24" t="n">
-        <v>0.08448576942804722</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P24" t="n">
-        <v>112.0514518896259</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q24" t="n">
-        <v>174.2141189579042</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_14_5_23</t>
+          <t>model_14_5_13</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9885749962375272</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C25" t="n">
-        <v>0.637731955177979</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9963138128405037</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E25" t="n">
-        <v>0.879287274273002</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9620813181883685</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00678237576786846</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2150579605710489</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I25" t="n">
-        <v>0.002879297958208851</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0392269582657617</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.02105313281787874</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01913463424559804</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M25" t="n">
-        <v>0.08235518057698896</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N25" t="n">
-        <v>1.010155558899976</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0858612111128772</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P25" t="n">
-        <v>111.9868556603366</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q25" t="n">
-        <v>174.1495227286148</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.988223457230901</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6367581660240409</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9961558978593779</v>
+        <v>0.9998037190799868</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8755683883992318</v>
+        <v>0.9999230701834255</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9608819399390042</v>
+        <v>0.9998580658845428</v>
       </c>
       <c r="G26" t="n">
-        <v>0.006991064507896125</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2156360438783277</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I26" t="n">
-        <v>0.003002646085434272</v>
+        <v>0.000109520792174774</v>
       </c>
       <c r="J26" t="n">
-        <v>0.04043545206860596</v>
+        <v>3.580323863520947e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.02171904915189533</v>
+        <v>7.266187932115235e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0193354239926879</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M26" t="n">
-        <v>0.08361258582232776</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N26" t="n">
-        <v>1.010468038016977</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O26" t="n">
-        <v>0.08717214670269775</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P26" t="n">
-        <v>111.926244888435</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q26" t="n">
-        <v>174.0889119567132</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
   </sheetData>
